--- a/nr-doc-core-body-structure/ig/StructureDefinition-fr-core-address.xlsx
+++ b/nr-doc-core-body-structure/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T12:10:10+00:00</t>
+    <t>2026-07-28T08:49:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-body-structure/ig/StructureDefinition-fr-core-address.xlsx
+++ b/nr-doc-core-body-structure/ig/StructureDefinition-fr-core-address.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T08:49:31+00:00</t>
+    <t>2026-07-28T09:03:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
